--- a/Unity/Assets/Config/Excel/Skill@技能配置/SkillConfig@cs.xlsx
+++ b/Unity/Assets/Config/Excel/Skill@技能配置/SkillConfig@cs.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14490" windowHeight="18360"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SkillConfig" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>Id</t>
   </si>
@@ -35,12 +35,18 @@
     <t>技能名称</t>
   </si>
   <si>
+    <t>技能Tag</t>
+  </si>
+  <si>
     <t>技能CD</t>
   </si>
   <si>
     <t>#Name</t>
   </si>
   <si>
+    <t>PlayerSkillTag</t>
+  </si>
+  <si>
     <t>CD</t>
   </si>
   <si>
@@ -50,10 +56,16 @@
     <t>string</t>
   </si>
   <si>
+    <t>PlayerSkillTagEnum</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>普通攻击</t>
+  </si>
+  <si>
+    <t>NormalAttack</t>
   </si>
 </sst>
 </file>
@@ -990,15 +1002,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:E9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A3:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="4" max="4" width="20.125" customWidth="1"/>
-    <col min="5" max="5" width="19.5" customWidth="1"/>
-    <col min="6" max="6" width="19.875" customWidth="1"/>
+    <col min="5" max="5" width="28.375" customWidth="1"/>
+    <col min="6" max="6" width="19.5" customWidth="1"/>
+    <col min="7" max="7" width="19.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" spans="3:5">
+    <row r="3" s="1" customFormat="1" spans="1:6">
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1008,56 +1021,70 @@
       <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="F3" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="3:5">
+    <row r="4" s="1" customFormat="1" spans="1:6">
       <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="3:5">
+    <row r="5" s="1" customFormat="1" spans="1:6">
       <c r="C5" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="2">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="2">
         <v>2000</v>
       </c>
     </row>
-    <row r="7" spans="3:5">
+    <row r="7" spans="1:6">
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:6">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
     </row>
-    <row r="9" spans="5:5">
-      <c r="E9" s="2"/>
+    <row r="9" spans="1:6">
+      <c r="F9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/Skill@技能配置/SkillConfig@cs.xlsx
+++ b/Unity/Assets/Config/Excel/Skill@技能配置/SkillConfig@cs.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>Id</t>
   </si>
@@ -50,6 +50,9 @@
     <t>CD</t>
   </si>
   <si>
+    <t>TestArr</t>
+  </si>
+  <si>
     <t>long</t>
   </si>
   <si>
@@ -62,10 +65,16 @@
     <t>int</t>
   </si>
   <si>
+    <t>int[]</t>
+  </si>
+  <si>
     <t>普通攻击</t>
   </si>
   <si>
     <t>NormalAttack</t>
+  </si>
+  <si>
+    <t>1|2|3|4</t>
   </si>
 </sst>
 </file>
@@ -1002,8 +1011,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A3:G9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="4" max="4" width="20.125" customWidth="1"/>
     <col min="5" max="5" width="28.375" customWidth="1"/>
@@ -1011,7 +1020,7 @@
     <col min="7" max="7" width="19.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" spans="1:6">
+    <row r="3" s="1" customFormat="1" spans="1:7">
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1025,7 +1034,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:6">
+    <row r="4" s="1" customFormat="1" spans="1:7">
       <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
@@ -1038,44 +1047,53 @@
       <c r="F4" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="G4" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:6">
+    <row r="5" s="1" customFormat="1" spans="1:7">
       <c r="C5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F6" s="2">
         <v>2000</v>
       </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:7">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1083,7 +1101,7 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7">
       <c r="F9" s="2"/>
     </row>
   </sheetData>

--- a/Unity/Assets/Config/Excel/Skill@技能配置/SkillConfig@cs.xlsx
+++ b/Unity/Assets/Config/Excel/Skill@技能配置/SkillConfig@cs.xlsx
@@ -1072,7 +1072,7 @@
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>13</v>
